--- a/data/trans_orig/P25C$parches_2023-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P25C$parches_2023-Provincia-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según método de dejar de fumar (multirrespuesta) en 2023</t>
+          <t>Población según método de dejar de fumar (multirrespuesta) en 2023 (tasa de respuesta: 99,69%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -735,7 +735,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4299</t>
+          <t>4080</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -750,7 +750,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>9,04%</t>
+          <t>8,58%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>885</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,32%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -805,7 +805,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>3725</t>
+          <t>3720</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -820,7 +820,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>6,24%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1422</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>885</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>7,32%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1284</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>1422</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>885</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>7,32%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1284</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -1069,12 +1069,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1422</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1104,12 +1104,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>885</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1119,12 +1119,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,32%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1139,12 +1139,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1284</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1154,12 +1154,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -1182,7 +1182,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>41678</t>
+          <t>43029</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1197,7 +1197,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>87,65%</t>
+          <t>90,49%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1217,7 +1217,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>11157</t>
+          <t>11137</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -1232,7 +1232,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>92,3%</t>
+          <t>92,13%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1252,12 +1252,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>54002</t>
+          <t>51927</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>59637</t>
+          <t>59574</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1267,12 +1267,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>90,55%</t>
+          <t>87,07%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>99,9%</t>
         </is>
       </c>
     </row>
@@ -1300,7 +1300,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>5871</t>
+          <t>4520</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1315,7 +1315,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>12,35%</t>
+          <t>9,51%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1335,7 +1335,7 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>3066</t>
+          <t>2880</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1350,7 +1350,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>25,36%</t>
+          <t>23,83%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1365,12 +1365,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>172</t>
+          <t>177</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>5596</t>
+          <t>6303</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1380,12 +1380,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>9,38%</t>
+          <t>10,57%</t>
         </is>
       </c>
     </row>
@@ -1408,12 +1408,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1422</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1423,12 +1423,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1443,12 +1443,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>885</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1458,12 +1458,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>7,32%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1478,12 +1478,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1284</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1493,12 +1493,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -1530,7 +1530,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>6324</t>
+          <t>4821</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1545,7 +1545,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1565,7 +1565,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>3471</t>
+          <t>3164</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1580,7 +1580,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1600,7 +1600,7 @@
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>7448</t>
+          <t>6264</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1615,7 +1615,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>3,56%</t>
         </is>
       </c>
     </row>
@@ -1638,12 +1638,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1998</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1653,12 +1653,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1678,7 +1678,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>3377</t>
+          <t>3192</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1693,7 +1693,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>4,88%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1713,7 +1713,7 @@
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>3041</t>
+          <t>3493</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1728,7 +1728,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,98%</t>
         </is>
       </c>
     </row>
@@ -1751,12 +1751,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1998</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1766,12 +1766,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1786,12 +1786,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1409</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1801,12 +1801,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1821,12 +1821,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1740</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1836,12 +1836,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -1864,12 +1864,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1998</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1879,12 +1879,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1904,7 +1904,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>4548</t>
+          <t>4307</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1919,7 +1919,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>6,95%</t>
+          <t>6,58%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1939,7 +1939,7 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>5197</t>
+          <t>4570</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1954,7 +1954,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>2,6%</t>
         </is>
       </c>
     </row>
@@ -1977,12 +1977,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>77979</t>
+          <t>79009</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>95920</t>
+          <t>96902</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1992,12 +1992,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>70,56%</t>
+          <t>71,49%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>86,79%</t>
+          <t>87,68%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2012,12 +2012,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>53193</t>
+          <t>52904</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>61730</t>
+          <t>61774</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2027,12 +2027,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>81,27%</t>
+          <t>80,83%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>94,32%</t>
+          <t>94,39%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2047,12 +2047,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>134984</t>
+          <t>135851</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>156092</t>
+          <t>155472</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>76,71%</t>
+          <t>77,2%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>88,71%</t>
+          <t>88,35%</t>
         </is>
       </c>
     </row>
@@ -2090,12 +2090,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>830</t>
+          <t>810</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>8840</t>
+          <t>9446</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2105,12 +2105,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>8,0%</t>
+          <t>8,55%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2125,12 +2125,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>678</t>
+          <t>675</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>5808</t>
+          <t>5838</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>8,87%</t>
+          <t>8,92%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2160,12 +2160,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2209</t>
+          <t>1680</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>11302</t>
+          <t>11654</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,42%</t>
+          <t>6,62%</t>
         </is>
       </c>
     </row>
@@ -2203,12 +2203,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>12197</t>
+          <t>11435</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>28927</t>
+          <t>27043</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2218,12 +2218,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>11,04%</t>
+          <t>10,35%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>26,18%</t>
+          <t>24,47%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2238,12 +2238,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>785</t>
+          <t>754</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>7010</t>
+          <t>7355</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>10,71%</t>
+          <t>11,24%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2273,12 +2273,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>13554</t>
+          <t>14053</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>31427</t>
+          <t>30994</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>7,99%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>17,86%</t>
+          <t>17,61%</t>
         </is>
       </c>
     </row>
@@ -2325,7 +2325,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>5629</t>
+          <t>5524</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2340,7 +2340,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>8,19%</t>
+          <t>8,04%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2355,12 +2355,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>447</t>
+          <t>462</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>4473</t>
+          <t>4417</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2370,12 +2370,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>9,04%</t>
+          <t>8,92%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2390,12 +2390,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>642</t>
+          <t>964</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>6562</t>
+          <t>7608</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2405,12 +2405,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>5,55%</t>
+          <t>6,43%</t>
         </is>
       </c>
     </row>
@@ -2433,12 +2433,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>1432</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2448,12 +2448,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2468,12 +2468,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>541</t>
+          <t>526</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>4996</t>
+          <t>4641</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>10,09%</t>
+          <t>9,38%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2503,12 +2503,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>568</t>
+          <t>552</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>4912</t>
+          <t>5072</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,29%</t>
         </is>
       </c>
     </row>
@@ -2546,12 +2546,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>1432</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2561,12 +2561,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2581,12 +2581,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1264</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2616,12 +2616,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1366</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -2659,12 +2659,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1432</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2674,12 +2674,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2699,7 +2699,7 @@
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>3020</t>
+          <t>3099</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2714,7 +2714,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>6,26%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2734,7 +2734,7 @@
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>3133</t>
+          <t>2604</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2749,7 +2749,7 @@
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,2%</t>
         </is>
       </c>
     </row>
@@ -2772,12 +2772,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>59084</t>
+          <t>59660</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>67788</t>
+          <t>67709</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2787,12 +2787,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>85,94%</t>
+          <t>86,78%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>98,6%</t>
+          <t>98,49%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2807,12 +2807,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>40513</t>
+          <t>40710</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>47224</t>
+          <t>47488</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2822,12 +2822,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>81,85%</t>
+          <t>82,25%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>95,41%</t>
+          <t>95,94%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>103100</t>
+          <t>103057</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>113425</t>
+          <t>113535</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2857,12 +2857,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>87,19%</t>
+          <t>87,16%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>95,93%</t>
+          <t>96,02%</t>
         </is>
       </c>
     </row>
@@ -2890,7 +2890,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>5257</t>
+          <t>4036</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2905,7 +2905,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>7,65%</t>
+          <t>5,87%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2925,7 +2925,7 @@
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>4613</t>
+          <t>4377</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2940,7 +2940,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>9,32%</t>
+          <t>8,84%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2955,12 +2955,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>651</t>
+          <t>687</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6175</t>
+          <t>5953</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2970,12 +2970,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>5,22%</t>
+          <t>5,03%</t>
         </is>
       </c>
     </row>
@@ -2998,12 +2998,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>619</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>8146</t>
+          <t>7698</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>11,85%</t>
+          <t>11,2%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3038,7 +3038,7 @@
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>3661</t>
+          <t>3779</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>7,4%</t>
+          <t>7,64%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3068,12 +3068,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1193</t>
+          <t>1289</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>8728</t>
+          <t>9342</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3083,12 +3083,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>7,38%</t>
+          <t>7,9%</t>
         </is>
       </c>
     </row>
@@ -3115,12 +3115,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1575</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3130,12 +3130,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3155,7 +3155,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>2637</t>
+          <t>2392</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3170,7 +3170,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>4,11%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3190,7 +3190,7 @@
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>2485</t>
+          <t>2395</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3205,7 +3205,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,57%</t>
         </is>
       </c>
     </row>
@@ -3233,7 +3233,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3274</t>
+          <t>3579</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3248,7 +3248,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3268,7 +3268,7 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>2397</t>
+          <t>2313</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3283,7 +3283,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3303,7 +3303,7 @@
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>3588</t>
+          <t>3779</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3318,7 +3318,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,48%</t>
         </is>
       </c>
     </row>
@@ -3346,7 +3346,7 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>6238</t>
+          <t>6520</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3361,7 +3361,7 @@
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>6,6%</t>
+          <t>6,9%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3376,12 +3376,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>1150</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3391,12 +3391,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3416,7 +3416,7 @@
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>6248</t>
+          <t>5608</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3431,7 +3431,7 @@
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>3,67%</t>
         </is>
       </c>
     </row>
@@ -3459,7 +3459,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>5518</t>
+          <t>5086</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3474,7 +3474,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>5,84%</t>
+          <t>5,38%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>514</t>
+          <t>513</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>4249</t>
+          <t>4672</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3509,7 +3509,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>8,03%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3524,12 +3524,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1027</t>
+          <t>719</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>7012</t>
+          <t>6835</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3539,12 +3539,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>4,48%</t>
         </is>
       </c>
     </row>
@@ -3567,12 +3567,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>65835</t>
+          <t>67395</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>83670</t>
+          <t>83238</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3582,12 +3582,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>69,69%</t>
+          <t>71,34%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>88,56%</t>
+          <t>88,11%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3602,12 +3602,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>47779</t>
+          <t>47609</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>54842</t>
+          <t>54839</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3617,12 +3617,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>82,11%</t>
+          <t>81,82%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>94,25%</t>
+          <t>94,24%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3637,12 +3637,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>117752</t>
+          <t>118667</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>135941</t>
+          <t>135777</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3652,12 +3652,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>77,13%</t>
+          <t>77,73%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>89,05%</t>
+          <t>88,94%</t>
         </is>
       </c>
     </row>
@@ -3680,12 +3680,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>8096</t>
+          <t>8044</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>25427</t>
+          <t>23623</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3695,12 +3695,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>8,57%</t>
+          <t>8,51%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>26,91%</t>
+          <t>25,0%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3715,12 +3715,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>1145</t>
+          <t>1346</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>6307</t>
+          <t>6378</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3730,12 +3730,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>10,84%</t>
+          <t>10,96%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3750,12 +3750,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>10772</t>
+          <t>10887</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>28544</t>
+          <t>27236</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3765,12 +3765,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>7,13%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>18,7%</t>
+          <t>17,84%</t>
         </is>
       </c>
     </row>
@@ -3793,12 +3793,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>1575</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3808,12 +3808,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3833,7 +3833,7 @@
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>3628</t>
+          <t>3599</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3848,7 +3848,7 @@
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>6,23%</t>
+          <t>6,18%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3868,7 +3868,7 @@
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>4143</t>
+          <t>2869</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3883,7 +3883,7 @@
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>1,88%</t>
         </is>
       </c>
     </row>
@@ -3910,12 +3910,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>1045</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3925,12 +3925,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3945,12 +3945,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>753</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3960,12 +3960,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>9,05%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3980,12 +3980,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>941</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3995,12 +3995,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -4023,12 +4023,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>1045</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4038,12 +4038,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -4058,12 +4058,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>753</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4073,12 +4073,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>9,05%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4093,12 +4093,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>941</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4108,12 +4108,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -4136,12 +4136,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>1045</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4151,12 +4151,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4176,7 +4176,7 @@
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>1668</t>
+          <t>1721</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4191,7 +4191,7 @@
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>20,03%</t>
+          <t>20,67%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4211,7 +4211,7 @@
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>2341</t>
+          <t>2256</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4226,7 +4226,7 @@
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>10,12%</t>
+          <t>9,75%</t>
         </is>
       </c>
     </row>
@@ -4249,12 +4249,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>1045</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4264,12 +4264,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4284,12 +4284,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>753</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4299,12 +4299,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>9,05%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4319,12 +4319,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>941</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4334,12 +4334,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -4362,12 +4362,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>13767</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>14812</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4377,12 +4377,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>92,94%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4397,7 +4397,7 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>6658</t>
+          <t>6605</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
@@ -4412,7 +4412,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>79,97%</t>
+          <t>79,33%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4432,7 +4432,7 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>20797</t>
+          <t>20882</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
@@ -4447,7 +4447,7 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>89,88%</t>
+          <t>90,25%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
@@ -4475,12 +4475,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>1045</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4490,12 +4490,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4510,12 +4510,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>753</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4525,12 +4525,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>9,05%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4545,12 +4545,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>941</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -4588,12 +4588,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>1045</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4603,12 +4603,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4623,12 +4623,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>753</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4638,12 +4638,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>9,05%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4658,12 +4658,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>941</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4673,12 +4673,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -4705,12 +4705,12 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>460</t>
+          <t>453</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>4441</t>
+          <t>4837</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -4720,12 +4720,12 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>9,79%</t>
+          <t>10,66%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -4740,12 +4740,12 @@
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>997</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>9,05%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>455</t>
+          <t>434</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>4634</t>
+          <t>4361</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>8,22%</t>
+          <t>7,73%</t>
         </is>
       </c>
     </row>
@@ -4818,12 +4818,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>1100</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4833,12 +4833,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4853,12 +4853,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>997</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -4868,12 +4868,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>9,05%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4888,12 +4888,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>1092</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4903,12 +4903,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -4936,7 +4936,7 @@
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>3155</t>
+          <t>3709</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4951,7 +4951,7 @@
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>6,95%</t>
+          <t>8,17%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4966,12 +4966,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>997</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -4981,12 +4981,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>9,05%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5006,7 +5006,7 @@
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>3208</t>
+          <t>2622</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -5021,7 +5021,7 @@
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>4,65%</t>
         </is>
       </c>
     </row>
@@ -5044,12 +5044,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>1100</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5059,12 +5059,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5079,12 +5079,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>997</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5094,12 +5094,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>9,05%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5114,12 +5114,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>1092</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5129,12 +5129,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -5157,12 +5157,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>40440</t>
+          <t>40582</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>44886</t>
+          <t>44847</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5172,12 +5172,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>89,11%</t>
+          <t>89,42%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>98,91%</t>
+          <t>98,82%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -5192,12 +5192,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>10027</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>11024</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -5207,12 +5207,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>90,95%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5227,12 +5227,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>51406</t>
+          <t>51467</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>55913</t>
+          <t>55958</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -5242,12 +5242,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>91,14%</t>
+          <t>91,24%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>99,13%</t>
+          <t>99,21%</t>
         </is>
       </c>
     </row>
@@ -5270,12 +5270,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>1100</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5285,12 +5285,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5305,12 +5305,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>997</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -5320,12 +5320,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>9,05%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5340,12 +5340,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>1092</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -5355,12 +5355,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -5383,12 +5383,12 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>1100</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
@@ -5418,12 +5418,12 @@
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>997</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -5433,12 +5433,12 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>9,05%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -5453,12 +5453,12 @@
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>1092</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
@@ -5468,12 +5468,12 @@
       </c>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -5505,7 +5505,7 @@
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>4156</t>
+          <t>3730</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -5520,7 +5520,7 @@
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -5535,12 +5535,12 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>1557</t>
+          <t>1773</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>7476</t>
+          <t>8312</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -5550,12 +5550,12 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>7,88%</t>
+          <t>8,77%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5570,12 +5570,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>2069</t>
+          <t>2062</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>9640</t>
+          <t>9066</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -5590,7 +5590,7 @@
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>4,18%</t>
         </is>
       </c>
     </row>
@@ -5613,12 +5613,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>723</t>
+          <t>729</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>7040</t>
+          <t>6570</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -5628,12 +5628,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>5,39%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -5648,12 +5648,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>638</t>
+          <t>625</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>6674</t>
+          <t>7392</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -5663,12 +5663,12 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>7,04%</t>
+          <t>7,8%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5683,12 +5683,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>2266</t>
+          <t>2082</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>10915</t>
+          <t>10417</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -5698,12 +5698,12 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>4,81%</t>
         </is>
       </c>
     </row>
@@ -5726,12 +5726,12 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>1623</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -5761,12 +5761,12 @@
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>1281</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -5776,12 +5776,12 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -5796,12 +5796,12 @@
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>1459</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
@@ -5811,12 +5811,12 @@
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -5844,7 +5844,7 @@
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>5257</t>
+          <t>4368</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -5859,7 +5859,7 @@
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -5874,12 +5874,12 @@
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>579</t>
+          <t>586</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>5030</t>
+          <t>5516</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -5889,12 +5889,12 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>5,82%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -5909,12 +5909,12 @@
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>826</t>
+          <t>800</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>6807</t>
+          <t>6915</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
@@ -5924,12 +5924,12 @@
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,19%</t>
         </is>
       </c>
     </row>
@@ -5952,12 +5952,12 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>108894</t>
+          <t>108849</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>118798</t>
+          <t>118480</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -5967,12 +5967,12 @@
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>89,39%</t>
+          <t>89,35%</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>97,52%</t>
+          <t>97,26%</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -5987,12 +5987,12 @@
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>78500</t>
+          <t>77870</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>88449</t>
+          <t>88753</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -6002,12 +6002,12 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>82,78%</t>
+          <t>82,12%</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>93,28%</t>
+          <t>93,6%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6022,12 +6022,12 @@
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>191066</t>
+          <t>191541</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>205248</t>
+          <t>205160</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
@@ -6037,12 +6037,12 @@
       </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>88,19%</t>
+          <t>88,41%</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>94,74%</t>
+          <t>94,7%</t>
         </is>
       </c>
     </row>
@@ -6070,7 +6070,7 @@
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>6148</t>
+          <t>6679</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
@@ -6085,7 +6085,7 @@
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>5,48%</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr">
@@ -6100,12 +6100,12 @@
       </c>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>628</t>
+          <t>773</t>
         </is>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>9018</t>
+          <t>8674</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
@@ -6115,12 +6115,12 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
         <is>
-          <t>9,51%</t>
+          <t>9,15%</t>
         </is>
       </c>
       <c r="Q51" s="2" t="inlineStr">
@@ -6135,12 +6135,12 @@
       </c>
       <c r="S51" s="2" t="inlineStr">
         <is>
-          <t>1652</t>
+          <t>1773</t>
         </is>
       </c>
       <c r="T51" s="2" t="inlineStr">
         <is>
-          <t>10893</t>
+          <t>11325</t>
         </is>
       </c>
       <c r="U51" s="2" t="inlineStr">
@@ -6150,12 +6150,12 @@
       </c>
       <c r="V51" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="W51" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>5,23%</t>
         </is>
       </c>
     </row>
@@ -6183,7 +6183,7 @@
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>3345</t>
+          <t>4806</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -6198,7 +6198,7 @@
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
@@ -6213,12 +6213,12 @@
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>1907</t>
+          <t>1835</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>8519</t>
+          <t>8651</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -6228,12 +6228,12 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>8,98%</t>
+          <t>9,12%</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -6248,12 +6248,12 @@
       </c>
       <c r="S52" s="2" t="inlineStr">
         <is>
-          <t>2552</t>
+          <t>2447</t>
         </is>
       </c>
       <c r="T52" s="2" t="inlineStr">
         <is>
-          <t>10214</t>
+          <t>9744</t>
         </is>
       </c>
       <c r="U52" s="2" t="inlineStr">
@@ -6263,12 +6263,12 @@
       </c>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>4,5%</t>
         </is>
       </c>
     </row>
@@ -6295,12 +6295,12 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>263</t>
+          <t>415</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>19253</t>
+          <t>18349</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -6310,12 +6310,12 @@
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>0,08%</t>
+          <t>0,12%</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>5,56%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
@@ -6330,12 +6330,12 @@
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>618</t>
+          <t>637</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>5630</t>
+          <t>5937</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -6345,12 +6345,12 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>14,8%</t>
+          <t>15,61%</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -6365,12 +6365,12 @@
       </c>
       <c r="S53" s="2" t="inlineStr">
         <is>
-          <t>980</t>
+          <t>901</t>
         </is>
       </c>
       <c r="T53" s="2" t="inlineStr">
         <is>
-          <t>22558</t>
+          <t>21850</t>
         </is>
       </c>
       <c r="U53" s="2" t="inlineStr">
@@ -6380,12 +6380,12 @@
       </c>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>5,87%</t>
+          <t>5,69%</t>
         </is>
       </c>
     </row>
@@ -6413,7 +6413,7 @@
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>6495</t>
+          <t>6540</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
@@ -6428,7 +6428,7 @@
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
@@ -6443,12 +6443,12 @@
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>1175</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -6458,12 +6458,12 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -6483,7 +6483,7 @@
       </c>
       <c r="T54" s="2" t="inlineStr">
         <is>
-          <t>7612</t>
+          <t>7615</t>
         </is>
       </c>
       <c r="U54" s="2" t="inlineStr">
@@ -6521,12 +6521,12 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>4710</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
@@ -6536,12 +6536,12 @@
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
@@ -6556,12 +6556,12 @@
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>1175</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
@@ -6571,12 +6571,12 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -6591,12 +6591,12 @@
       </c>
       <c r="S55" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T55" s="2" t="inlineStr">
         <is>
-          <t>3650</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U55" s="2" t="inlineStr">
@@ -6606,12 +6606,12 @@
       </c>
       <c r="V55" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -6639,7 +6639,7 @@
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>8335</t>
+          <t>8284</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
@@ -6654,7 +6654,7 @@
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
@@ -6674,7 +6674,7 @@
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>2906</t>
+          <t>3093</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -6689,7 +6689,7 @@
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>7,64%</t>
+          <t>8,13%</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -6709,7 +6709,7 @@
       </c>
       <c r="T56" s="2" t="inlineStr">
         <is>
-          <t>8296</t>
+          <t>8386</t>
         </is>
       </c>
       <c r="U56" s="2" t="inlineStr">
@@ -6724,7 +6724,7 @@
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,18%</t>
         </is>
       </c>
     </row>
@@ -6747,12 +6747,12 @@
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>306670</t>
+          <t>307525</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>344683</t>
+          <t>344798</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
@@ -6762,12 +6762,12 @@
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>88,57%</t>
+          <t>88,82%</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>99,55%</t>
+          <t>99,58%</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr">
@@ -6782,12 +6782,12 @@
       </c>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>30547</t>
+          <t>30598</t>
         </is>
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>36769</t>
+          <t>36724</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
@@ -6797,12 +6797,12 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>80,29%</t>
+          <t>80,42%</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
         <is>
-          <t>96,64%</t>
+          <t>96,52%</t>
         </is>
       </c>
       <c r="Q57" s="2" t="inlineStr">
@@ -6817,12 +6817,12 @@
       </c>
       <c r="S57" s="2" t="inlineStr">
         <is>
-          <t>342928</t>
+          <t>342777</t>
         </is>
       </c>
       <c r="T57" s="2" t="inlineStr">
         <is>
-          <t>381872</t>
+          <t>382121</t>
         </is>
       </c>
       <c r="U57" s="2" t="inlineStr">
@@ -6832,12 +6832,12 @@
       </c>
       <c r="V57" s="2" t="inlineStr">
         <is>
-          <t>89,24%</t>
+          <t>89,2%</t>
         </is>
       </c>
       <c r="W57" s="2" t="inlineStr">
         <is>
-          <t>99,37%</t>
+          <t>99,43%</t>
         </is>
       </c>
     </row>
@@ -6865,7 +6865,7 @@
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>11053</t>
+          <t>10855</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
@@ -6880,7 +6880,7 @@
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr">
@@ -6895,12 +6895,12 @@
       </c>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>1175</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
@@ -6910,12 +6910,12 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q58" s="2" t="inlineStr">
@@ -6935,7 +6935,7 @@
       </c>
       <c r="T58" s="2" t="inlineStr">
         <is>
-          <t>8767</t>
+          <t>9794</t>
         </is>
       </c>
       <c r="U58" s="2" t="inlineStr">
@@ -6950,7 +6950,7 @@
       </c>
       <c r="W58" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,55%</t>
         </is>
       </c>
     </row>
@@ -6978,7 +6978,7 @@
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>9147</t>
+          <t>9238</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
@@ -6993,7 +6993,7 @@
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr">
@@ -7013,7 +7013,7 @@
       </c>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>3552</t>
+          <t>3573</t>
         </is>
       </c>
       <c r="N59" s="2" t="inlineStr">
@@ -7028,7 +7028,7 @@
       </c>
       <c r="P59" s="2" t="inlineStr">
         <is>
-          <t>9,33%</t>
+          <t>9,39%</t>
         </is>
       </c>
       <c r="Q59" s="2" t="inlineStr">
@@ -7048,7 +7048,7 @@
       </c>
       <c r="T59" s="2" t="inlineStr">
         <is>
-          <t>9206</t>
+          <t>10010</t>
         </is>
       </c>
       <c r="U59" s="2" t="inlineStr">
@@ -7063,7 +7063,7 @@
       </c>
       <c r="W59" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,6%</t>
         </is>
       </c>
     </row>
@@ -7090,12 +7090,12 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>3049</t>
+          <t>3734</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>17496</t>
+          <t>18064</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
@@ -7105,12 +7105,12 @@
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr">
@@ -7125,12 +7125,12 @@
       </c>
       <c r="L60" s="2" t="inlineStr">
         <is>
-          <t>5339</t>
+          <t>5403</t>
         </is>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>14595</t>
+          <t>15018</t>
         </is>
       </c>
       <c r="N60" s="2" t="inlineStr">
@@ -7140,12 +7140,12 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,45%</t>
         </is>
       </c>
       <c r="Q60" s="2" t="inlineStr">
@@ -7160,12 +7160,12 @@
       </c>
       <c r="S60" s="2" t="inlineStr">
         <is>
-          <t>9330</t>
+          <t>9443</t>
         </is>
       </c>
       <c r="T60" s="2" t="inlineStr">
         <is>
-          <t>28718</t>
+          <t>28695</t>
         </is>
       </c>
       <c r="U60" s="2" t="inlineStr">
@@ -7175,7 +7175,7 @@
       </c>
       <c r="V60" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="W60" s="2" t="inlineStr">
@@ -7203,12 +7203,12 @@
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>924</t>
+          <t>813</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>9494</t>
+          <t>9829</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
@@ -7218,12 +7218,12 @@
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>0,11%</t>
+          <t>0,1%</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr">
@@ -7238,12 +7238,12 @@
       </c>
       <c r="L61" s="2" t="inlineStr">
         <is>
-          <t>2315</t>
+          <t>2433</t>
         </is>
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>10430</t>
+          <t>10200</t>
         </is>
       </c>
       <c r="N61" s="2" t="inlineStr">
@@ -7253,12 +7253,12 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="Q61" s="2" t="inlineStr">
@@ -7273,12 +7273,12 @@
       </c>
       <c r="S61" s="2" t="inlineStr">
         <is>
-          <t>4000</t>
+          <t>3881</t>
         </is>
       </c>
       <c r="T61" s="2" t="inlineStr">
         <is>
-          <t>16557</t>
+          <t>16540</t>
         </is>
       </c>
       <c r="U61" s="2" t="inlineStr">
@@ -7288,7 +7288,7 @@
       </c>
       <c r="V61" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="W61" s="2" t="inlineStr">
@@ -7321,7 +7321,7 @@
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>6642</t>
+          <t>7332</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
@@ -7336,7 +7336,7 @@
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr">
@@ -7356,7 +7356,7 @@
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>2565</t>
+          <t>1917</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
@@ -7371,7 +7371,7 @@
       </c>
       <c r="P62" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="Q62" s="2" t="inlineStr">
@@ -7386,12 +7386,12 @@
       </c>
       <c r="S62" s="2" t="inlineStr">
         <is>
-          <t>500</t>
+          <t>701</t>
         </is>
       </c>
       <c r="T62" s="2" t="inlineStr">
         <is>
-          <t>7838</t>
+          <t>7321</t>
         </is>
       </c>
       <c r="U62" s="2" t="inlineStr">
@@ -7401,12 +7401,12 @@
       </c>
       <c r="V62" s="2" t="inlineStr">
         <is>
-          <t>0,04%</t>
+          <t>0,06%</t>
         </is>
       </c>
       <c r="W62" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,62%</t>
         </is>
       </c>
     </row>
@@ -7429,12 +7429,12 @@
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>832</t>
+          <t>834</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>9049</t>
+          <t>9150</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
@@ -7449,7 +7449,7 @@
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="J63" s="2" t="inlineStr">
@@ -7464,12 +7464,12 @@
       </c>
       <c r="L63" s="2" t="inlineStr">
         <is>
-          <t>3141</t>
+          <t>3137</t>
         </is>
       </c>
       <c r="M63" s="2" t="inlineStr">
         <is>
-          <t>10839</t>
+          <t>11316</t>
         </is>
       </c>
       <c r="N63" s="2" t="inlineStr">
@@ -7484,7 +7484,7 @@
       </c>
       <c r="P63" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="Q63" s="2" t="inlineStr">
@@ -7499,12 +7499,12 @@
       </c>
       <c r="S63" s="2" t="inlineStr">
         <is>
-          <t>4438</t>
+          <t>4726</t>
         </is>
       </c>
       <c r="T63" s="2" t="inlineStr">
         <is>
-          <t>16629</t>
+          <t>16793</t>
         </is>
       </c>
       <c r="U63" s="2" t="inlineStr">
@@ -7514,12 +7514,12 @@
       </c>
       <c r="V63" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="W63" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,41%</t>
         </is>
       </c>
     </row>
@@ -7542,12 +7542,12 @@
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>753362</t>
+          <t>753183</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>824064</t>
+          <t>824349</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
@@ -7557,12 +7557,12 @@
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>88,68%</t>
+          <t>88,66%</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>97,0%</t>
+          <t>97,03%</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr">
@@ -7577,12 +7577,12 @@
       </c>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t>294702</t>
+          <t>294116</t>
         </is>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>311951</t>
+          <t>311532</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr">
@@ -7592,12 +7592,12 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>87,33%</t>
+          <t>87,16%</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
         <is>
-          <t>92,45%</t>
+          <t>92,32%</t>
         </is>
       </c>
       <c r="Q64" s="2" t="inlineStr">
@@ -7612,12 +7612,12 @@
       </c>
       <c r="S64" s="2" t="inlineStr">
         <is>
-          <t>1058013</t>
+          <t>1056936</t>
         </is>
       </c>
       <c r="T64" s="2" t="inlineStr">
         <is>
-          <t>1138617</t>
+          <t>1136007</t>
         </is>
       </c>
       <c r="U64" s="2" t="inlineStr">
@@ -7627,12 +7627,12 @@
       </c>
       <c r="V64" s="2" t="inlineStr">
         <is>
-          <t>89,13%</t>
+          <t>89,04%</t>
         </is>
       </c>
       <c r="W64" s="2" t="inlineStr">
         <is>
-          <t>95,92%</t>
+          <t>95,7%</t>
         </is>
       </c>
     </row>
@@ -7655,12 +7655,12 @@
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>8387</t>
+          <t>8218</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>40205</t>
+          <t>38177</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
@@ -7670,12 +7670,12 @@
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr">
@@ -7690,12 +7690,12 @@
       </c>
       <c r="L65" s="2" t="inlineStr">
         <is>
-          <t>5844</t>
+          <t>6096</t>
         </is>
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>18144</t>
+          <t>16891</t>
         </is>
       </c>
       <c r="N65" s="2" t="inlineStr">
@@ -7705,12 +7705,12 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>5,01%</t>
         </is>
       </c>
       <c r="Q65" s="2" t="inlineStr">
@@ -7725,12 +7725,12 @@
       </c>
       <c r="S65" s="2" t="inlineStr">
         <is>
-          <t>15660</t>
+          <t>17238</t>
         </is>
       </c>
       <c r="T65" s="2" t="inlineStr">
         <is>
-          <t>49324</t>
+          <t>49429</t>
         </is>
       </c>
       <c r="U65" s="2" t="inlineStr">
@@ -7740,7 +7740,7 @@
       </c>
       <c r="V65" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="W65" s="2" t="inlineStr">
@@ -7768,12 +7768,12 @@
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>8461</t>
+          <t>8153</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>39834</t>
+          <t>40995</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
@@ -7783,12 +7783,12 @@
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="J66" s="2" t="inlineStr">
@@ -7803,12 +7803,12 @@
       </c>
       <c r="L66" s="2" t="inlineStr">
         <is>
-          <t>5309</t>
+          <t>5282</t>
         </is>
       </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>15816</t>
+          <t>15108</t>
         </is>
       </c>
       <c r="N66" s="2" t="inlineStr">
@@ -7823,7 +7823,7 @@
       </c>
       <c r="P66" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>4,48%</t>
         </is>
       </c>
       <c r="Q66" s="2" t="inlineStr">
@@ -7838,12 +7838,12 @@
       </c>
       <c r="S66" s="2" t="inlineStr">
         <is>
-          <t>16853</t>
+          <t>17537</t>
         </is>
       </c>
       <c r="T66" s="2" t="inlineStr">
         <is>
-          <t>48026</t>
+          <t>49645</t>
         </is>
       </c>
       <c r="U66" s="2" t="inlineStr">
@@ -7853,12 +7853,12 @@
       </c>
       <c r="V66" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="W66" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>4,18%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P25C$parches_2023-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P25C$parches_2023-Provincia-trans_orig.xlsx
@@ -725,7 +725,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>806</t>
+          <t>681</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -735,12 +735,12 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4080</t>
+          <t>4670</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -750,7 +750,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>8,58%</t>
+          <t>9,27%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -795,7 +795,7 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>806</t>
+          <t>681</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
@@ -805,12 +805,12 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>3720</t>
+          <t>3115</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
@@ -820,7 +820,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>4,96%</t>
         </is>
       </c>
     </row>
@@ -1177,27 +1177,27 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>46546</t>
+          <t>49496</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>43029</t>
+          <t>45937</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>47549</t>
+          <t>50361</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>97,89%</t>
+          <t>98,28%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>90,49%</t>
+          <t>91,22%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1212,27 +1212,27 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>11922</t>
+          <t>11882</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>11137</t>
+          <t>9731</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>12088</t>
+          <t>12436</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>98,63%</t>
+          <t>95,54%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>92,13%</t>
+          <t>78,24%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1247,32 +1247,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>58468</t>
+          <t>61378</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>51927</t>
+          <t>57698</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>59574</t>
+          <t>62797</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>98,04%</t>
+          <t>97,74%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>87,07%</t>
+          <t>91,88%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,9%</t>
+          <t>100,0%</t>
         </is>
       </c>
     </row>
@@ -1290,7 +1290,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1003</t>
+          <t>865</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -1300,12 +1300,12 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>4520</t>
+          <t>4424</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -1315,7 +1315,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>9,51%</t>
+          <t>8,78%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1325,7 +1325,7 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>761</t>
+          <t>1119</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
@@ -1335,12 +1335,12 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2880</t>
+          <t>3542</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>6,29%</t>
+          <t>9,0%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
@@ -1350,7 +1350,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>23,83%</t>
+          <t>28,48%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1360,32 +1360,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>1763</t>
+          <t>1985</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>177</t>
+          <t>556</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>6303</t>
+          <t>6171</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>10,57%</t>
+          <t>9,83%</t>
         </is>
       </c>
     </row>
@@ -1520,7 +1520,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1029</t>
+          <t>1003</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1530,12 +1530,12 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4821</t>
+          <t>5163</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1545,7 +1545,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1555,7 +1555,7 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>643</t>
+          <t>665</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
@@ -1565,12 +1565,12 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>3164</t>
+          <t>3408</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
@@ -1580,7 +1580,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>5,11%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1590,7 +1590,7 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1673</t>
+          <t>1668</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
@@ -1600,12 +1600,12 @@
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>6264</t>
+          <t>5800</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
@@ -1615,7 +1615,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,13%</t>
         </is>
       </c>
     </row>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>593</t>
+          <t>609</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
@@ -1678,7 +1678,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>3192</t>
+          <t>3469</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1693,7 +1693,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>5,2%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1703,7 +1703,7 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>593</t>
+          <t>609</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
@@ -1713,12 +1713,12 @@
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>3493</t>
+          <t>3501</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
@@ -1728,7 +1728,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>1,89%</t>
         </is>
       </c>
     </row>
@@ -1894,7 +1894,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>1457</t>
+          <t>1448</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
@@ -1904,12 +1904,12 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>4307</t>
+          <t>5063</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
@@ -1919,7 +1919,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>6,58%</t>
+          <t>7,59%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1929,7 +1929,7 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1457</t>
+          <t>1448</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
@@ -1939,12 +1939,12 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>4570</t>
+          <t>5040</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
@@ -1954,7 +1954,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,72%</t>
         </is>
       </c>
     </row>
@@ -1972,32 +1972,32 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>88242</t>
+          <t>93165</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>79009</t>
+          <t>82485</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>96902</t>
+          <t>101214</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>79,85%</t>
+          <t>78,55%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>71,49%</t>
+          <t>69,55%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>87,68%</t>
+          <t>85,34%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2007,32 +2007,32 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>58402</t>
+          <t>59727</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>52904</t>
+          <t>54061</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>61774</t>
+          <t>63192</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>89,23%</t>
+          <t>89,49%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>80,83%</t>
+          <t>81,0%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>94,39%</t>
+          <t>94,68%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2042,32 +2042,32 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>146645</t>
+          <t>152892</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>135851</t>
+          <t>142276</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>155472</t>
+          <t>162888</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>83,34%</t>
+          <t>82,49%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>77,2%</t>
+          <t>76,76%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>88,35%</t>
+          <t>87,88%</t>
         </is>
       </c>
     </row>
@@ -2085,32 +2085,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>3152</t>
+          <t>3269</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>810</t>
+          <t>890</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>9446</t>
+          <t>8871</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>8,55%</t>
+          <t>7,48%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2120,32 +2120,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>2155</t>
+          <t>2117</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>675</t>
+          <t>683</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>5838</t>
+          <t>5787</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>8,92%</t>
+          <t>8,67%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2155,32 +2155,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>5307</t>
+          <t>5385</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1680</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>11654</t>
+          <t>11103</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,62%</t>
+          <t>5,99%</t>
         </is>
       </c>
     </row>
@@ -2198,32 +2198,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>18949</t>
+          <t>22098</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>11435</t>
+          <t>14763</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>27043</t>
+          <t>31949</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>17,15%</t>
+          <t>18,63%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>10,35%</t>
+          <t>12,45%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>24,47%</t>
+          <t>26,94%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2233,32 +2233,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>2917</t>
+          <t>2882</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>754</t>
+          <t>953</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>7355</t>
+          <t>7426</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>11,24%</t>
+          <t>11,13%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2268,32 +2268,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>21867</t>
+          <t>24980</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>14053</t>
+          <t>16580</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>30994</t>
+          <t>35436</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>12,43%</t>
+          <t>13,48%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>7,99%</t>
+          <t>8,95%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>17,61%</t>
+          <t>19,12%</t>
         </is>
       </c>
     </row>
@@ -2315,7 +2315,7 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>997</t>
+          <t>926</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -2325,12 +2325,12 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>5524</t>
+          <t>4550</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
@@ -2340,7 +2340,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>8,04%</t>
+          <t>6,72%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2350,32 +2350,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>1679</t>
+          <t>1712</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>462</t>
+          <t>510</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>4417</t>
+          <t>4543</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>8,92%</t>
+          <t>9,15%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2385,32 +2385,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>2677</t>
+          <t>2638</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>964</t>
+          <t>634</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>7608</t>
+          <t>6378</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>5,44%</t>
         </is>
       </c>
     </row>
@@ -2463,32 +2463,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>1843</t>
+          <t>1886</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>526</t>
+          <t>569</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>4641</t>
+          <t>5068</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>9,38%</t>
+          <t>10,21%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2498,32 +2498,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>1843</t>
+          <t>1886</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>552</t>
+          <t>584</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>5072</t>
+          <t>5220</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>4,45%</t>
         </is>
       </c>
     </row>
@@ -2689,7 +2689,7 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>564</t>
+          <t>590</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
@@ -2699,12 +2699,12 @@
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>3099</t>
+          <t>3225</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
@@ -2714,7 +2714,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>6,5%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2724,7 +2724,7 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>564</t>
+          <t>590</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
@@ -2734,12 +2734,12 @@
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>2604</t>
+          <t>3166</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
@@ -2749,7 +2749,7 @@
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,7%</t>
         </is>
       </c>
     </row>
@@ -2767,32 +2767,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>64932</t>
+          <t>64020</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>59660</t>
+          <t>58447</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>67709</t>
+          <t>66470</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>94,45%</t>
+          <t>94,58%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>86,78%</t>
+          <t>86,35%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>98,49%</t>
+          <t>98,2%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2802,32 +2802,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>44544</t>
+          <t>44635</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>40710</t>
+          <t>40492</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>47488</t>
+          <t>47239</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>89,99%</t>
+          <t>89,93%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>82,25%</t>
+          <t>81,58%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>95,94%</t>
+          <t>95,17%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2837,32 +2837,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>109475</t>
+          <t>108655</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>103057</t>
+          <t>102108</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>113535</t>
+          <t>112358</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>92,59%</t>
+          <t>92,61%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>87,16%</t>
+          <t>87,03%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>96,02%</t>
+          <t>95,77%</t>
         </is>
       </c>
     </row>
@@ -2880,7 +2880,7 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>947</t>
+          <t>911</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
@@ -2890,12 +2890,12 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>4036</t>
+          <t>4955</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
@@ -2905,7 +2905,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>5,87%</t>
+          <t>7,32%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2915,7 +2915,7 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>1376</t>
+          <t>1387</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
@@ -2925,12 +2925,12 @@
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>4377</t>
+          <t>4849</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
@@ -2940,7 +2940,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>8,84%</t>
+          <t>9,77%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2950,17 +2950,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>2322</t>
+          <t>2298</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>687</t>
+          <t>674</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>5953</t>
+          <t>6288</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2970,12 +2970,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>5,36%</t>
         </is>
       </c>
     </row>
@@ -2993,32 +2993,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>2868</t>
+          <t>2757</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>619</t>
+          <t>870</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>7698</t>
+          <t>8361</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,07%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>11,2%</t>
+          <t>12,35%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3028,7 +3028,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>694</t>
+          <t>677</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>3779</t>
+          <t>3461</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>7,64%</t>
+          <t>6,97%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3063,32 +3063,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>3562</t>
+          <t>3434</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1289</t>
+          <t>1225</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>9342</t>
+          <t>8422</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>7,9%</t>
+          <t>7,18%</t>
         </is>
       </c>
     </row>
@@ -3145,7 +3145,7 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>457</t>
+          <t>498</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
@@ -3155,12 +3155,12 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>2392</t>
+          <t>2830</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
@@ -3170,7 +3170,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3180,7 +3180,7 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>457</t>
+          <t>498</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
@@ -3190,12 +3190,12 @@
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>2395</t>
+          <t>2593</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
@@ -3205,7 +3205,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,5%</t>
         </is>
       </c>
     </row>
@@ -3223,7 +3223,7 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>582</t>
+          <t>587</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
@@ -3233,12 +3233,12 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3579</t>
+          <t>3185</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
@@ -3248,7 +3248,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3258,7 +3258,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>458</t>
+          <t>498</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
@@ -3268,12 +3268,12 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>2313</t>
+          <t>2397</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
@@ -3283,7 +3283,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3293,7 +3293,7 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>1040</t>
+          <t>1085</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
@@ -3303,12 +3303,12 @@
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>3779</t>
+          <t>3332</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
@@ -3318,7 +3318,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>1,93%</t>
         </is>
       </c>
     </row>
@@ -3336,7 +3336,7 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>1695</t>
+          <t>1655</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
@@ -3346,12 +3346,12 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>6520</t>
+          <t>5558</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
@@ -3361,7 +3361,7 @@
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>6,9%</t>
+          <t>5,17%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3406,7 +3406,7 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>1695</t>
+          <t>1655</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
@@ -3416,12 +3416,12 @@
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>5608</t>
+          <t>6481</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
@@ -3431,7 +3431,7 @@
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,76%</t>
         </is>
       </c>
     </row>
@@ -3449,7 +3449,7 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>1195</t>
+          <t>1944</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
@@ -3459,12 +3459,12 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>5086</t>
+          <t>7369</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
@@ -3474,7 +3474,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>6,86%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3484,32 +3484,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>1617</t>
+          <t>1702</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>513</t>
+          <t>538</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>4672</t>
+          <t>4616</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>8,03%</t>
+          <t>7,09%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3519,32 +3519,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>2812</t>
+          <t>3646</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>719</t>
+          <t>1162</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>6835</t>
+          <t>8441</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>4,89%</t>
         </is>
       </c>
     </row>
@@ -3562,32 +3562,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>76690</t>
+          <t>88229</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>67395</t>
+          <t>78085</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>83238</t>
+          <t>96068</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>81,18%</t>
+          <t>82,13%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>71,34%</t>
+          <t>72,68%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>88,11%</t>
+          <t>89,42%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3597,32 +3597,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>51926</t>
+          <t>58551</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>47609</t>
+          <t>53993</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>54839</t>
+          <t>61540</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>89,23%</t>
+          <t>89,95%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>81,82%</t>
+          <t>82,95%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>94,24%</t>
+          <t>94,54%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3632,32 +3632,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>128615</t>
+          <t>146780</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>118667</t>
+          <t>136130</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>135777</t>
+          <t>154727</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>84,25%</t>
+          <t>85,08%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>77,73%</t>
+          <t>78,9%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>88,94%</t>
+          <t>89,68%</t>
         </is>
       </c>
     </row>
@@ -3675,32 +3675,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>14312</t>
+          <t>15016</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>8044</t>
+          <t>8097</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>23623</t>
+          <t>24983</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>15,15%</t>
+          <t>13,98%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>8,51%</t>
+          <t>7,54%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>23,25%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3710,32 +3710,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>3029</t>
+          <t>3114</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>1346</t>
+          <t>1274</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>6378</t>
+          <t>6858</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>5,21%</t>
+          <t>4,78%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>10,96%</t>
+          <t>10,54%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3745,32 +3745,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>17341</t>
+          <t>18130</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>10887</t>
+          <t>10763</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>27236</t>
+          <t>28122</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>11,36%</t>
+          <t>10,51%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>7,13%</t>
+          <t>6,24%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>17,84%</t>
+          <t>16,3%</t>
         </is>
       </c>
     </row>
@@ -3823,7 +3823,7 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>704</t>
+          <t>731</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
@@ -3833,12 +3833,12 @@
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>3599</t>
+          <t>4361</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
@@ -3848,7 +3848,7 @@
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3858,7 +3858,7 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>704</t>
+          <t>731</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>2869</t>
+          <t>3688</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
@@ -3883,7 +3883,7 @@
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>2,14%</t>
         </is>
       </c>
     </row>
@@ -4166,7 +4166,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>377</t>
+          <t>389</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
@@ -4176,12 +4176,12 @@
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>1721</t>
+          <t>2137</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
@@ -4191,7 +4191,7 @@
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>20,67%</t>
+          <t>24,2%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4201,7 +4201,7 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>377</t>
+          <t>389</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
@@ -4211,12 +4211,12 @@
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>2256</t>
+          <t>1698</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
@@ -4226,7 +4226,7 @@
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>9,75%</t>
+          <t>6,92%</t>
         </is>
       </c>
     </row>
@@ -4357,7 +4357,7 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>14812</t>
+          <t>15697</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
@@ -4392,27 +4392,27 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>7949</t>
+          <t>8443</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>6605</t>
+          <t>6695</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>8326</t>
+          <t>8832</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>95,47%</t>
+          <t>95,6%</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>79,33%</t>
+          <t>75,8%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4427,27 +4427,27 @@
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>22761</t>
+          <t>24140</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>20882</t>
+          <t>22831</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>23138</t>
+          <t>24529</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t>98,37%</t>
+          <t>98,41%</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>90,25%</t>
+          <t>93,08%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
@@ -4700,32 +4700,32 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>1847</t>
+          <t>1863</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>453</t>
+          <t>489</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>4837</t>
+          <t>4614</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>10,66%</t>
+          <t>10,36%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -4770,32 +4770,32 @@
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t>1847</t>
+          <t>1863</t>
         </is>
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>434</t>
+          <t>500</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>4361</t>
+          <t>4792</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>7,73%</t>
+          <t>8,55%</t>
         </is>
       </c>
     </row>
@@ -4926,7 +4926,7 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>636</t>
+          <t>624</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
@@ -4936,7 +4936,7 @@
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>3709</t>
+          <t>3056</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4951,7 +4951,7 @@
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>8,17%</t>
+          <t>6,86%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4996,7 +4996,7 @@
       </c>
       <c r="R41" s="2" t="inlineStr">
         <is>
-          <t>636</t>
+          <t>624</t>
         </is>
       </c>
       <c r="S41" s="2" t="inlineStr">
@@ -5006,12 +5006,12 @@
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>2622</t>
+          <t>4024</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="V41" s="2" t="inlineStr">
@@ -5021,7 +5021,7 @@
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>7,18%</t>
         </is>
       </c>
     </row>
@@ -5152,32 +5152,32 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>43365</t>
+          <t>42526</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>40582</t>
+          <t>39976</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>44847</t>
+          <t>44034</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>95,55%</t>
+          <t>95,49%</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>89,42%</t>
+          <t>89,76%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>98,82%</t>
+          <t>98,87%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -5187,7 +5187,7 @@
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>11024</t>
+          <t>11500</t>
         </is>
       </c>
       <c r="L43" s="2" t="inlineStr">
@@ -5222,32 +5222,32 @@
       </c>
       <c r="R43" s="2" t="inlineStr">
         <is>
-          <t>54389</t>
+          <t>54026</t>
         </is>
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>51467</t>
+          <t>50831</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>55958</t>
+          <t>55424</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
         <is>
-          <t>96,42%</t>
+          <t>96,41%</t>
         </is>
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>91,24%</t>
+          <t>90,71%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>99,21%</t>
+          <t>98,91%</t>
         </is>
       </c>
     </row>
@@ -5495,7 +5495,7 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>759</t>
+          <t>819</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
@@ -5505,12 +5505,12 @@
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>3730</t>
+          <t>3741</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
@@ -5520,7 +5520,7 @@
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -5530,32 +5530,32 @@
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>3972</t>
+          <t>4793</t>
         </is>
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>1773</t>
+          <t>2040</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>8312</t>
+          <t>9692</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,46%</t>
         </is>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>8,77%</t>
+          <t>9,02%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5565,32 +5565,32 @@
       </c>
       <c r="R46" s="2" t="inlineStr">
         <is>
-          <t>4732</t>
+          <t>5612</t>
         </is>
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>2062</t>
+          <t>2705</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>9066</t>
+          <t>10306</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>4,13%</t>
         </is>
       </c>
     </row>
@@ -5608,32 +5608,32 @@
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>2573</t>
+          <t>2957</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>729</t>
+          <t>808</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>6570</t>
+          <t>8465</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>5,95%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -5643,32 +5643,32 @@
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>2459</t>
+          <t>3097</t>
         </is>
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>625</t>
+          <t>682</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>7392</t>
+          <t>7689</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>7,8%</t>
+          <t>7,16%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5678,32 +5678,32 @@
       </c>
       <c r="R47" s="2" t="inlineStr">
         <is>
-          <t>5033</t>
+          <t>6053</t>
         </is>
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>2082</t>
+          <t>2710</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>10417</t>
+          <t>12098</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>4,84%</t>
         </is>
       </c>
     </row>
@@ -5834,7 +5834,7 @@
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>878</t>
+          <t>971</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
@@ -5844,12 +5844,12 @@
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>4368</t>
+          <t>6297</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
@@ -5859,7 +5859,7 @@
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>4,42%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -5869,32 +5869,32 @@
       </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
-          <t>2005</t>
+          <t>2738</t>
         </is>
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>586</t>
+          <t>708</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>5516</t>
+          <t>6487</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>6,04%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -5904,32 +5904,32 @@
       </c>
       <c r="R49" s="2" t="inlineStr">
         <is>
-          <t>2883</t>
+          <t>3709</t>
         </is>
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>800</t>
+          <t>1375</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>6915</t>
+          <t>8381</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,36%</t>
         </is>
       </c>
     </row>
@@ -5947,32 +5947,32 @@
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>115049</t>
+          <t>134740</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>108849</t>
+          <t>128057</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>118480</t>
+          <t>139026</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>94,44%</t>
+          <t>94,65%</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>89,35%</t>
+          <t>89,95%</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>97,26%</t>
+          <t>97,66%</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -5982,32 +5982,32 @@
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>84118</t>
+          <t>95407</t>
         </is>
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>77870</t>
+          <t>88603</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>88753</t>
+          <t>100140</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
-          <t>88,71%</t>
+          <t>88,83%</t>
         </is>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>82,12%</t>
+          <t>82,49%</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>93,6%</t>
+          <t>93,23%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6017,27 +6017,27 @@
       </c>
       <c r="R50" s="2" t="inlineStr">
         <is>
-          <t>199166</t>
+          <t>230147</t>
         </is>
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>191541</t>
+          <t>221864</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>205160</t>
+          <t>236534</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
         <is>
-          <t>91,93%</t>
+          <t>92,14%</t>
         </is>
       </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>88,41%</t>
+          <t>88,83%</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
@@ -6060,7 +6060,7 @@
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>1846</t>
+          <t>2001</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
@@ -6070,12 +6070,12 @@
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>6679</t>
+          <t>6536</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
@@ -6085,7 +6085,7 @@
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>5,48%</t>
+          <t>4,59%</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr">
@@ -6095,32 +6095,32 @@
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
-          <t>3001</t>
+          <t>3761</t>
         </is>
       </c>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>773</t>
+          <t>1318</t>
         </is>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>8674</t>
+          <t>11997</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
         <is>
-          <t>9,15%</t>
+          <t>11,17%</t>
         </is>
       </c>
       <c r="Q51" s="2" t="inlineStr">
@@ -6130,32 +6130,32 @@
       </c>
       <c r="R51" s="2" t="inlineStr">
         <is>
-          <t>4847</t>
+          <t>5762</t>
         </is>
       </c>
       <c r="S51" s="2" t="inlineStr">
         <is>
-          <t>1773</t>
+          <t>2227</t>
         </is>
       </c>
       <c r="T51" s="2" t="inlineStr">
         <is>
-          <t>11325</t>
+          <t>12051</t>
         </is>
       </c>
       <c r="U51" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="V51" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="W51" s="2" t="inlineStr">
         <is>
-          <t>5,23%</t>
+          <t>4,82%</t>
         </is>
       </c>
     </row>
@@ -6173,7 +6173,7 @@
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>718</t>
+          <t>871</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
@@ -6183,12 +6183,12 @@
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>4806</t>
+          <t>4460</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
@@ -6198,7 +6198,7 @@
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
@@ -6208,32 +6208,32 @@
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>4455</t>
+          <t>4817</t>
         </is>
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>1835</t>
+          <t>2056</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>8651</t>
+          <t>9123</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,48%</t>
         </is>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>9,12%</t>
+          <t>8,49%</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -6243,32 +6243,32 @@
       </c>
       <c r="R52" s="2" t="inlineStr">
         <is>
-          <t>5173</t>
+          <t>5688</t>
         </is>
       </c>
       <c r="S52" s="2" t="inlineStr">
         <is>
-          <t>2447</t>
+          <t>2684</t>
         </is>
       </c>
       <c r="T52" s="2" t="inlineStr">
         <is>
-          <t>9744</t>
+          <t>10748</t>
         </is>
       </c>
       <c r="U52" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>4,3%</t>
         </is>
       </c>
     </row>
@@ -6290,32 +6290,32 @@
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>4628</t>
+          <t>5053</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>415</t>
+          <t>2102</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>18349</t>
+          <t>10431</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>4,45%</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>0,12%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>9,19%</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
@@ -6325,32 +6325,32 @@
       </c>
       <c r="K53" s="2" t="inlineStr">
         <is>
-          <t>2487</t>
+          <t>2790</t>
         </is>
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>637</t>
+          <t>719</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>5937</t>
+          <t>6492</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
         <is>
-          <t>6,54%</t>
+          <t>6,31%</t>
         </is>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>15,61%</t>
+          <t>14,67%</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -6360,32 +6360,32 @@
       </c>
       <c r="R53" s="2" t="inlineStr">
         <is>
-          <t>7115</t>
+          <t>7843</t>
         </is>
       </c>
       <c r="S53" s="2" t="inlineStr">
         <is>
-          <t>901</t>
+          <t>4219</t>
         </is>
       </c>
       <c r="T53" s="2" t="inlineStr">
         <is>
-          <t>21850</t>
+          <t>13823</t>
         </is>
       </c>
       <c r="U53" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>4,97%</t>
         </is>
       </c>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>8,76%</t>
         </is>
       </c>
     </row>
@@ -6403,7 +6403,7 @@
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>942</t>
+          <t>1041</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
@@ -6413,12 +6413,12 @@
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>6540</t>
+          <t>5810</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
@@ -6428,7 +6428,7 @@
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>5,12%</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
@@ -6473,7 +6473,7 @@
       </c>
       <c r="R54" s="2" t="inlineStr">
         <is>
-          <t>942</t>
+          <t>1041</t>
         </is>
       </c>
       <c r="S54" s="2" t="inlineStr">
@@ -6483,12 +6483,12 @@
       </c>
       <c r="T54" s="2" t="inlineStr">
         <is>
-          <t>7615</t>
+          <t>6115</t>
         </is>
       </c>
       <c r="U54" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="V54" s="2" t="inlineStr">
@@ -6498,7 +6498,7 @@
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>3,88%</t>
         </is>
       </c>
     </row>
@@ -6629,32 +6629,32 @@
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>1820</t>
+          <t>2008</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>647</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>8284</t>
+          <t>5467</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>4,82%</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
@@ -6664,7 +6664,7 @@
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>551</t>
+          <t>615</t>
         </is>
       </c>
       <c r="L56" s="2" t="inlineStr">
@@ -6674,12 +6674,12 @@
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>3093</t>
+          <t>2525</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="O56" s="2" t="inlineStr">
@@ -6689,7 +6689,7 @@
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>8,13%</t>
+          <t>5,71%</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -6699,32 +6699,32 @@
       </c>
       <c r="R56" s="2" t="inlineStr">
         <is>
-          <t>2371</t>
+          <t>2623</t>
         </is>
       </c>
       <c r="S56" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>683</t>
         </is>
       </c>
       <c r="T56" s="2" t="inlineStr">
         <is>
-          <t>8386</t>
+          <t>6689</t>
         </is>
       </c>
       <c r="U56" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="V56" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>4,24%</t>
         </is>
       </c>
     </row>
@@ -6742,32 +6742,32 @@
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>336401</t>
+          <t>102782</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>307525</t>
+          <t>95906</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>344798</t>
+          <t>107377</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>97,16%</t>
+          <t>90,52%</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>88,82%</t>
+          <t>84,47%</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>99,58%</t>
+          <t>94,57%</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr">
@@ -6777,32 +6777,32 @@
       </c>
       <c r="K57" s="2" t="inlineStr">
         <is>
-          <t>34312</t>
+          <t>40056</t>
         </is>
       </c>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>30598</t>
+          <t>36134</t>
         </is>
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>36724</t>
+          <t>42406</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
         <is>
-          <t>90,18%</t>
+          <t>90,54%</t>
         </is>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>80,42%</t>
+          <t>81,68%</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
         <is>
-          <t>96,52%</t>
+          <t>95,85%</t>
         </is>
       </c>
       <c r="Q57" s="2" t="inlineStr">
@@ -6812,32 +6812,32 @@
       </c>
       <c r="R57" s="2" t="inlineStr">
         <is>
-          <t>370712</t>
+          <t>142838</t>
         </is>
       </c>
       <c r="S57" s="2" t="inlineStr">
         <is>
-          <t>342777</t>
+          <t>134807</t>
         </is>
       </c>
       <c r="T57" s="2" t="inlineStr">
         <is>
-          <t>382121</t>
+          <t>147971</t>
         </is>
       </c>
       <c r="U57" s="2" t="inlineStr">
         <is>
-          <t>96,46%</t>
+          <t>90,53%</t>
         </is>
       </c>
       <c r="V57" s="2" t="inlineStr">
         <is>
-          <t>89,2%</t>
+          <t>85,44%</t>
         </is>
       </c>
       <c r="W57" s="2" t="inlineStr">
         <is>
-          <t>99,43%</t>
+          <t>93,78%</t>
         </is>
       </c>
     </row>
@@ -6855,32 +6855,32 @@
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>2236</t>
+          <t>2368</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>664</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>10855</t>
+          <t>7074</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>6,23%</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr">
@@ -6925,32 +6925,32 @@
       </c>
       <c r="R58" s="2" t="inlineStr">
         <is>
-          <t>2236</t>
+          <t>2368</t>
         </is>
       </c>
       <c r="S58" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>666</t>
         </is>
       </c>
       <c r="T58" s="2" t="inlineStr">
         <is>
-          <t>9794</t>
+          <t>6693</t>
         </is>
       </c>
       <c r="U58" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="V58" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="W58" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>4,24%</t>
         </is>
       </c>
     </row>
@@ -6968,7 +6968,7 @@
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>1761</t>
+          <t>1979</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
@@ -6978,12 +6978,12 @@
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>9238</t>
+          <t>6997</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
@@ -6993,7 +6993,7 @@
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>6,16%</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr">
@@ -7003,7 +7003,7 @@
       </c>
       <c r="K59" s="2" t="inlineStr">
         <is>
-          <t>697</t>
+          <t>781</t>
         </is>
       </c>
       <c r="L59" s="2" t="inlineStr">
@@ -7013,12 +7013,12 @@
       </c>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>3573</t>
+          <t>3836</t>
         </is>
       </c>
       <c r="N59" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="O59" s="2" t="inlineStr">
@@ -7028,7 +7028,7 @@
       </c>
       <c r="P59" s="2" t="inlineStr">
         <is>
-          <t>9,39%</t>
+          <t>8,67%</t>
         </is>
       </c>
       <c r="Q59" s="2" t="inlineStr">
@@ -7038,32 +7038,32 @@
       </c>
       <c r="R59" s="2" t="inlineStr">
         <is>
-          <t>2458</t>
+          <t>2760</t>
         </is>
       </c>
       <c r="S59" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>777</t>
         </is>
       </c>
       <c r="T59" s="2" t="inlineStr">
         <is>
-          <t>10010</t>
+          <t>7587</t>
         </is>
       </c>
       <c r="U59" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="V59" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="W59" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>4,81%</t>
         </is>
       </c>
     </row>
@@ -7085,32 +7085,32 @@
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>10066</t>
+          <t>10345</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>3734</t>
+          <t>5849</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>18064</t>
+          <t>16906</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr">
@@ -7120,32 +7120,32 @@
       </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
-          <t>9239</t>
+          <t>10457</t>
         </is>
       </c>
       <c r="L60" s="2" t="inlineStr">
         <is>
-          <t>5403</t>
+          <t>5797</t>
         </is>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>15018</t>
+          <t>16122</t>
         </is>
       </c>
       <c r="N60" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>4,41%</t>
         </is>
       </c>
       <c r="Q60" s="2" t="inlineStr">
@@ -7155,32 +7155,32 @@
       </c>
       <c r="R60" s="2" t="inlineStr">
         <is>
-          <t>19306</t>
+          <t>20802</t>
         </is>
       </c>
       <c r="S60" s="2" t="inlineStr">
         <is>
-          <t>9443</t>
+          <t>14291</t>
         </is>
       </c>
       <c r="T60" s="2" t="inlineStr">
         <is>
-          <t>28695</t>
+          <t>28574</t>
         </is>
       </c>
       <c r="U60" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="V60" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="W60" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,78%</t>
         </is>
       </c>
     </row>
@@ -7198,32 +7198,32 @@
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>4097</t>
+          <t>4585</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>813</t>
+          <t>1634</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>9829</t>
+          <t>10624</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>0,1%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr">
@@ -7233,32 +7233,32 @@
       </c>
       <c r="K61" s="2" t="inlineStr">
         <is>
-          <t>5353</t>
+          <t>6089</t>
         </is>
       </c>
       <c r="L61" s="2" t="inlineStr">
         <is>
-          <t>2433</t>
+          <t>2877</t>
         </is>
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>10200</t>
+          <t>11632</t>
         </is>
       </c>
       <c r="N61" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="Q61" s="2" t="inlineStr">
@@ -7268,32 +7268,32 @@
       </c>
       <c r="R61" s="2" t="inlineStr">
         <is>
-          <t>9449</t>
+          <t>10674</t>
         </is>
       </c>
       <c r="S61" s="2" t="inlineStr">
         <is>
-          <t>3881</t>
+          <t>6087</t>
         </is>
       </c>
       <c r="T61" s="2" t="inlineStr">
         <is>
-          <t>16540</t>
+          <t>17349</t>
         </is>
       </c>
       <c r="U61" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="V61" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="W61" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,69%</t>
         </is>
       </c>
     </row>
@@ -7311,32 +7311,32 @@
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>2331</t>
+          <t>2279</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>573</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>7332</t>
+          <t>7275</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,09%</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr">
@@ -7346,7 +7346,7 @@
       </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
-          <t>377</t>
+          <t>389</t>
         </is>
       </c>
       <c r="L62" s="2" t="inlineStr">
@@ -7356,7 +7356,7 @@
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>1917</t>
+          <t>1844</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
@@ -7371,7 +7371,7 @@
       </c>
       <c r="P62" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="Q62" s="2" t="inlineStr">
@@ -7381,22 +7381,22 @@
       </c>
       <c r="R62" s="2" t="inlineStr">
         <is>
-          <t>2708</t>
+          <t>2668</t>
         </is>
       </c>
       <c r="S62" s="2" t="inlineStr">
         <is>
-          <t>701</t>
+          <t>627</t>
         </is>
       </c>
       <c r="T62" s="2" t="inlineStr">
         <is>
-          <t>7321</t>
+          <t>6792</t>
         </is>
       </c>
       <c r="U62" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="V62" s="2" t="inlineStr">
@@ -7406,7 +7406,7 @@
       </c>
       <c r="W62" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,66%</t>
         </is>
       </c>
     </row>
@@ -7424,32 +7424,32 @@
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>3893</t>
+          <t>4923</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>834</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>9150</t>
+          <t>10157</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>0,1%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="J63" s="2" t="inlineStr">
@@ -7459,27 +7459,27 @@
       </c>
       <c r="K63" s="2" t="inlineStr">
         <is>
-          <t>6194</t>
+          <t>7092</t>
         </is>
       </c>
       <c r="L63" s="2" t="inlineStr">
         <is>
-          <t>3137</t>
+          <t>3902</t>
         </is>
       </c>
       <c r="M63" s="2" t="inlineStr">
         <is>
-          <t>11316</t>
+          <t>12254</t>
         </is>
       </c>
       <c r="N63" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7494,32 +7494,32 @@
       </c>
       <c r="R63" s="2" t="inlineStr">
         <is>
-          <t>10086</t>
+          <t>12016</t>
         </is>
       </c>
       <c r="S63" s="2" t="inlineStr">
         <is>
-          <t>4726</t>
+          <t>7383</t>
         </is>
       </c>
       <c r="T63" s="2" t="inlineStr">
         <is>
-          <t>16793</t>
+          <t>19530</t>
         </is>
       </c>
       <c r="U63" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="V63" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="W63" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,9%</t>
         </is>
       </c>
     </row>
@@ -7537,32 +7537,32 @@
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>786038</t>
+          <t>590654</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>753183</t>
+          <t>571253</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>824349</t>
+          <t>605462</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>92,52%</t>
+          <t>89,46%</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>88,66%</t>
+          <t>86,52%</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>97,03%</t>
+          <t>91,71%</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr">
@@ -7572,32 +7572,32 @@
       </c>
       <c r="K64" s="2" t="inlineStr">
         <is>
-          <t>304194</t>
+          <t>330202</t>
         </is>
       </c>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t>294116</t>
+          <t>320890</t>
         </is>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>311532</t>
+          <t>339402</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr">
         <is>
-          <t>90,15%</t>
+          <t>90,25%</t>
         </is>
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>87,16%</t>
+          <t>87,7%</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
         <is>
-          <t>92,32%</t>
+          <t>92,76%</t>
         </is>
       </c>
       <c r="Q64" s="2" t="inlineStr">
@@ -7607,32 +7607,32 @@
       </c>
       <c r="R64" s="2" t="inlineStr">
         <is>
-          <t>1090232</t>
+          <t>920856</t>
         </is>
       </c>
       <c r="S64" s="2" t="inlineStr">
         <is>
-          <t>1056936</t>
+          <t>901378</t>
         </is>
       </c>
       <c r="T64" s="2" t="inlineStr">
         <is>
-          <t>1136007</t>
+          <t>938614</t>
         </is>
       </c>
       <c r="U64" s="2" t="inlineStr">
         <is>
-          <t>91,85%</t>
+          <t>89,74%</t>
         </is>
       </c>
       <c r="V64" s="2" t="inlineStr">
         <is>
-          <t>89,04%</t>
+          <t>87,84%</t>
         </is>
       </c>
       <c r="W64" s="2" t="inlineStr">
         <is>
-          <t>95,7%</t>
+          <t>91,47%</t>
         </is>
       </c>
     </row>
@@ -7650,32 +7650,32 @@
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>23495</t>
+          <t>24430</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>8218</t>
+          <t>15407</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>38177</t>
+          <t>36890</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>5,59%</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr">
@@ -7685,32 +7685,32 @@
       </c>
       <c r="K65" s="2" t="inlineStr">
         <is>
-          <t>10322</t>
+          <t>11498</t>
         </is>
       </c>
       <c r="L65" s="2" t="inlineStr">
         <is>
-          <t>6096</t>
+          <t>6448</t>
         </is>
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>16891</t>
+          <t>18308</t>
         </is>
       </c>
       <c r="N65" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="Q65" s="2" t="inlineStr">
@@ -7720,32 +7720,32 @@
       </c>
       <c r="R65" s="2" t="inlineStr">
         <is>
-          <t>33817</t>
+          <t>35928</t>
         </is>
       </c>
       <c r="S65" s="2" t="inlineStr">
         <is>
-          <t>17238</t>
+          <t>25587</t>
         </is>
       </c>
       <c r="T65" s="2" t="inlineStr">
         <is>
-          <t>49429</t>
+          <t>50963</t>
         </is>
       </c>
       <c r="U65" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="V65" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="W65" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>4,97%</t>
         </is>
       </c>
     </row>
@@ -7763,32 +7763,32 @@
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>24296</t>
+          <t>27705</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>8153</t>
+          <t>18024</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>40995</t>
+          <t>40558</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>6,14%</t>
         </is>
       </c>
       <c r="J66" s="2" t="inlineStr">
@@ -7798,32 +7798,32 @@
       </c>
       <c r="K66" s="2" t="inlineStr">
         <is>
-          <t>9467</t>
+          <t>9888</t>
         </is>
       </c>
       <c r="L66" s="2" t="inlineStr">
         <is>
-          <t>5282</t>
+          <t>5310</t>
         </is>
       </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>15108</t>
+          <t>15779</t>
         </is>
       </c>
       <c r="N66" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="Q66" s="2" t="inlineStr">
@@ -7833,32 +7833,32 @@
       </c>
       <c r="R66" s="2" t="inlineStr">
         <is>
-          <t>33763</t>
+          <t>37593</t>
         </is>
       </c>
       <c r="S66" s="2" t="inlineStr">
         <is>
-          <t>17537</t>
+          <t>27280</t>
         </is>
       </c>
       <c r="T66" s="2" t="inlineStr">
         <is>
-          <t>49645</t>
+          <t>50816</t>
         </is>
       </c>
       <c r="U66" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="V66" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="W66" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>4,95%</t>
         </is>
       </c>
     </row>
